--- a/e2e/fixtures/annan-butik.xlsx
+++ b/e2e/fixtures/annan-butik.xlsx
@@ -7,6 +7,27 @@
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
+    <font/>
+  </fonts>
+  <fills count="1">
+    <fill/>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0"/>
+    <xf numFmtId="14" applyNumberFormat="1"/>
+  </cellXfs>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
@@ -48,20 +69,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
+      <c r="A2" s="1">
+        <v>45866</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C2">
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -85,20 +102,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-07-21</t>
-        </is>
+      <c r="A3" s="1">
+        <v>45859</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -122,20 +135,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-07-20</t>
-        </is>
+      <c r="A4" s="1">
+        <v>45858</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C4">
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -159,20 +168,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
+      <c r="A5" s="1">
+        <v>45847</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C5">
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -196,20 +201,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-07-14</t>
-        </is>
+      <c r="A6" s="1">
+        <v>45852</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C6">
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -233,20 +234,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-07-11</t>
-        </is>
+      <c r="A7" s="1">
+        <v>45849</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C7">
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -270,20 +267,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
+      <c r="A8" s="1">
+        <v>45853</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C8">
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -307,20 +300,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-07-12</t>
-        </is>
+      <c r="A9" s="1">
+        <v>45850</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C9">
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -344,20 +333,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025-07-12</t>
-        </is>
+      <c r="A10" s="1">
+        <v>45850</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C10">
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -381,20 +366,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
+      <c r="A11" s="1">
+        <v>45845</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C11">
+        <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -418,20 +399,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
-        </is>
+      <c r="A12" s="1">
+        <v>45848</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C12">
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -455,20 +432,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2025-07-05</t>
-        </is>
+      <c r="A13" s="1">
+        <v>45843</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C13">
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -492,20 +465,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2025-07-11</t>
-        </is>
+      <c r="A14" s="1">
+        <v>45849</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C14">
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -529,20 +498,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025-07-17</t>
-        </is>
+      <c r="A15" s="1">
+        <v>45855</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C15">
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -566,20 +531,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2025-07-11</t>
-        </is>
+      <c r="A16" s="1">
+        <v>45849</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C16">
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -603,20 +564,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
+      <c r="A17" s="1">
+        <v>45860</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C17">
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -640,20 +597,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
+      <c r="A18" s="1">
+        <v>45856</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C18">
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -677,20 +630,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2025-07-03</t>
-        </is>
+      <c r="A19" s="1">
+        <v>45841</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C19">
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -714,20 +663,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2025-07-13</t>
-        </is>
+      <c r="A20" s="1">
+        <v>45851</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C20">
+        <v>4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -751,20 +696,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2025-07-06</t>
-        </is>
+      <c r="A21" s="1">
+        <v>45844</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C21">
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -788,20 +729,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
+      <c r="A22" s="1">
+        <v>45854</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C22">
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -825,20 +762,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
+      <c r="A23" s="1">
+        <v>45847</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C23">
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -862,20 +795,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
+      <c r="A24" s="1">
+        <v>45897</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C24">
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -899,20 +828,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2025-08-15</t>
-        </is>
+      <c r="A25" s="1">
+        <v>45884</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C25">
+        <v>4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -936,20 +861,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2025-08-09</t>
-        </is>
+      <c r="A26" s="1">
+        <v>45878</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C26">
+        <v>4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -973,20 +894,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
+      <c r="A27" s="1">
+        <v>45886</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C27">
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1010,20 +927,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
+      <c r="A28" s="1">
+        <v>45890</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C28">
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1047,20 +960,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
+      <c r="A29" s="1">
+        <v>45894</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C29">
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1084,20 +993,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
+      <c r="A30" s="1">
+        <v>45873</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C30">
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1121,20 +1026,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
+      <c r="A31" s="1">
+        <v>45871</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C31">
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1158,20 +1059,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
+      <c r="A32" s="1">
+        <v>45894</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C32">
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1195,20 +1092,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
+      <c r="A33" s="1">
+        <v>45883</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C33">
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1232,20 +1125,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
+      <c r="A34" s="1">
+        <v>45881</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C34">
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1269,20 +1158,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
+      <c r="A35" s="1">
+        <v>45870</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C35">
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1306,20 +1191,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
+      <c r="A36" s="1">
+        <v>45886</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C36">
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1343,20 +1224,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2025-08-24</t>
-        </is>
+      <c r="A37" s="1">
+        <v>45893</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C37">
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1380,20 +1257,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2025-08-16</t>
-        </is>
+      <c r="A38" s="1">
+        <v>45885</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C38">
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1417,20 +1290,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2025-08-20</t>
-        </is>
+      <c r="A39" s="1">
+        <v>45889</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C39">
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1454,20 +1323,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
+      <c r="A40" s="1">
+        <v>45887</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C40">
+        <v>4</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1491,20 +1356,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
+      <c r="A41" s="1">
+        <v>45891</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C41">
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1528,20 +1389,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
+      <c r="A42" s="1">
+        <v>45870</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C42">
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1565,20 +1422,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
+      <c r="A43" s="1">
+        <v>45890</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C43">
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1602,20 +1455,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
+      <c r="A44" s="1">
+        <v>45888</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C44">
+        <v>4</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1639,20 +1488,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2025-09-28</t>
-        </is>
+      <c r="A45" s="1">
+        <v>45928</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C45">
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1676,20 +1521,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
+      <c r="A46" s="1">
+        <v>45912</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C46">
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1713,20 +1554,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
+      <c r="A47" s="1">
+        <v>45911</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C47">
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1750,20 +1587,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
+      <c r="A48" s="1">
+        <v>45912</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C48">
+        <v>4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1787,20 +1620,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
+      <c r="A49" s="1">
+        <v>45923</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C49">
+        <v>4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1824,20 +1653,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
+      <c r="A50" s="1">
+        <v>45912</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C50">
+        <v>4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1861,20 +1686,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2025-09-07</t>
-        </is>
+      <c r="A51" s="1">
+        <v>45907</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C51">
+        <v>4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1898,20 +1719,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2025-09-03</t>
-        </is>
+      <c r="A52" s="1">
+        <v>45903</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C52">
+        <v>3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1935,20 +1752,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
+      <c r="A53" s="1">
+        <v>45908</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C53">
+        <v>3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1972,20 +1785,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
+      <c r="A54" s="1">
+        <v>45913</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C54">
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2009,20 +1818,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
+      <c r="A55" s="1">
+        <v>45915</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C55">
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2046,20 +1851,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
+      <c r="A56" s="1">
+        <v>45909</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C56">
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2083,20 +1884,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
+      <c r="A57" s="1">
+        <v>45910</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C57">
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2120,20 +1917,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
+      <c r="A58" s="1">
+        <v>45916</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C58">
+        <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2157,20 +1950,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
+      <c r="A59" s="1">
+        <v>45918</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C59">
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2194,20 +1983,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
+      <c r="A60" s="1">
+        <v>45910</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C60">
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2231,20 +2016,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
+      <c r="A61" s="1">
+        <v>45910</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C61">
+        <v>4</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2268,20 +2049,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
+      <c r="A62" s="1">
+        <v>45905</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C62">
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2305,20 +2082,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
+      <c r="A63" s="1">
+        <v>45902</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C63">
+        <v>3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2342,20 +2115,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
+      <c r="A64" s="1">
+        <v>45912</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C64">
+        <v>4</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2379,20 +2148,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
+      <c r="A65" s="1">
+        <v>45923</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C65">
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2416,20 +2181,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
+      <c r="A66" s="1">
+        <v>45911</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C66">
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2453,20 +2214,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
+      <c r="A67" s="1">
+        <v>45958</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C67">
+        <v>3</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2490,20 +2247,16 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
+      <c r="A68" s="1">
+        <v>45937</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C68">
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2527,20 +2280,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2025-10-18</t>
-        </is>
+      <c r="A69" s="1">
+        <v>45948</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C69">
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2564,20 +2313,16 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
+      <c r="A70" s="1">
+        <v>45943</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C70">
+        <v>3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2601,20 +2346,16 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2025-10-05</t>
-        </is>
+      <c r="A71" s="1">
+        <v>45935</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C71">
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2638,20 +2379,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
+      <c r="A72" s="1">
+        <v>45953</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C72">
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2675,20 +2412,16 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
+      <c r="A73" s="1">
+        <v>45953</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C73">
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2712,20 +2445,16 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
+      <c r="A74" s="1">
+        <v>45953</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C74">
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2749,20 +2478,16 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
+      <c r="A75" s="1">
+        <v>45944</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C75">
+        <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2786,20 +2511,16 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
+      <c r="A76" s="1">
+        <v>45956</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C76">
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2823,20 +2544,16 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2025-10-19</t>
-        </is>
+      <c r="A77" s="1">
+        <v>45949</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C77">
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2860,20 +2577,16 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2025-10-05</t>
-        </is>
+      <c r="A78" s="1">
+        <v>45935</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C78">
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2897,20 +2610,16 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
+      <c r="A79" s="1">
+        <v>45937</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C79">
+        <v>4</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2934,20 +2643,16 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2025-10-25</t>
-        </is>
+      <c r="A80" s="1">
+        <v>45955</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C80">
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2971,20 +2676,16 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
+      <c r="A81" s="1">
+        <v>45941</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C81">
+        <v>4</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3008,20 +2709,16 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
+      <c r="A82" s="1">
+        <v>45956</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C82">
+        <v>3</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3045,20 +2742,16 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
+      <c r="A83" s="1">
+        <v>45946</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C83">
+        <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3082,20 +2775,16 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2025-10-10</t>
-        </is>
+      <c r="A84" s="1">
+        <v>45940</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C84">
+        <v>3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3119,20 +2808,16 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
+      <c r="A85" s="1">
+        <v>45945</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C85">
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3156,20 +2841,16 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
+      <c r="A86" s="1">
+        <v>45941</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C86">
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3193,20 +2874,16 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2025-10-03</t>
-        </is>
+      <c r="A87" s="1">
+        <v>45933</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C87">
+        <v>4</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3230,20 +2907,16 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
+      <c r="A88" s="1">
+        <v>45989</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C88">
+        <v>4</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3267,20 +2940,16 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
+      <c r="A89" s="1">
+        <v>45973</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C89">
+        <v>3</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3304,20 +2973,16 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2025-11-15</t>
-        </is>
+      <c r="A90" s="1">
+        <v>45976</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C90">
+        <v>4</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3341,20 +3006,16 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
+      <c r="A91" s="1">
+        <v>45965</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C91">
+        <v>4</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3378,20 +3039,16 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
+      <c r="A92" s="1">
+        <v>45968</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C92">
+        <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3415,20 +3072,16 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
+      <c r="A93" s="1">
+        <v>45982</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C93">
+        <v>2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3452,20 +3105,16 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
+      <c r="A94" s="1">
+        <v>45979</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C94">
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3489,20 +3138,16 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
+      <c r="A95" s="1">
+        <v>45964</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C95">
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3526,20 +3171,16 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
+      <c r="A96" s="1">
+        <v>45977</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C96">
+        <v>3</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3563,20 +3204,16 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
+      <c r="A97" s="1">
+        <v>45986</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C97">
+        <v>4</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3600,20 +3237,16 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
+      <c r="A98" s="1">
+        <v>45970</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C98">
+        <v>3</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3637,20 +3270,16 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
+      <c r="A99" s="1">
+        <v>45983</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C99">
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3674,20 +3303,16 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
+      <c r="A100" s="1">
+        <v>45974</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C100">
+        <v>3</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3711,20 +3336,16 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
+      <c r="A101" s="1">
+        <v>45979</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C101">
+        <v>4</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3748,20 +3369,16 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
+      <c r="A102" s="1">
+        <v>45987</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C102">
+        <v>4</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -3785,20 +3402,16 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
+      <c r="A103" s="1">
+        <v>45987</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C103">
+        <v>2</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3822,20 +3435,16 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
+      <c r="A104" s="1">
+        <v>45970</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C104">
+        <v>3</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3859,20 +3468,16 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
+      <c r="A105" s="1">
+        <v>45967</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C105">
+        <v>3</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3896,20 +3501,16 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
+      <c r="A106" s="1">
+        <v>45962</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C106">
+        <v>4</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3933,20 +3534,16 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2025-11-15</t>
-        </is>
+      <c r="A107" s="1">
+        <v>45976</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C107">
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3970,20 +3567,16 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
+      <c r="A108" s="1">
+        <v>45980</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C108">
+        <v>1</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -4007,20 +3600,16 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
+      <c r="A109" s="1">
+        <v>45962</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C109">
+        <v>4</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -4044,20 +3633,16 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
-        </is>
+      <c r="A110" s="1">
+        <v>46019</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C110">
+        <v>1</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -4081,20 +3666,16 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
+      <c r="A111" s="1">
+        <v>45995</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C111">
+        <v>3</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -4118,20 +3699,16 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
+      <c r="A112" s="1">
+        <v>45999</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C112">
+        <v>2</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -4155,20 +3732,16 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
+      <c r="A113" s="1">
+        <v>46009</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C113">
+        <v>3</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -4192,20 +3765,16 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
+      <c r="A114" s="1">
+        <v>45998</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C114">
+        <v>4</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -4229,20 +3798,16 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
+      <c r="A115" s="1">
+        <v>45997</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C115">
+        <v>2</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4266,20 +3831,16 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
+      <c r="A116" s="1">
+        <v>46007</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C116">
+        <v>2</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -4303,20 +3864,16 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2025-12-21</t>
-        </is>
+      <c r="A117" s="1">
+        <v>46012</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C117">
+        <v>2</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -4340,20 +3897,16 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
+      <c r="A118" s="1">
+        <v>46002</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C118">
+        <v>3</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -4377,20 +3930,16 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
+      <c r="A119" s="1">
+        <v>46007</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C119">
+        <v>4</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -4414,20 +3963,16 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
+      <c r="A120" s="1">
+        <v>46000</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C120">
+        <v>4</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -4451,20 +3996,16 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
+      <c r="A121" s="1">
+        <v>46007</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C121">
+        <v>2</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -4488,20 +4029,16 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
+      <c r="A122" s="1">
+        <v>46006</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C122">
+        <v>3</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4525,20 +4062,16 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
+      <c r="A123" s="1">
+        <v>46009</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C123">
+        <v>1</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4562,20 +4095,16 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
+      <c r="A124" s="1">
+        <v>46015</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C124">
+        <v>2</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -4599,20 +4128,16 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
+      <c r="A125" s="1">
+        <v>45998</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C125">
+        <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -4636,20 +4161,16 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
+      <c r="A126" s="1">
+        <v>45995</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C126">
+        <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -4673,20 +4194,16 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
+      <c r="A127" s="1">
+        <v>46002</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C127">
+        <v>2</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -4710,20 +4227,16 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
+      <c r="A128" s="1">
+        <v>45996</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C128">
+        <v>2</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4747,20 +4260,16 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
+      <c r="A129" s="1">
+        <v>46014</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C129">
+        <v>3</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4784,20 +4293,16 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
+      <c r="A130" s="1">
+        <v>45999</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C130">
+        <v>2</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4821,20 +4326,16 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
+      <c r="A131" s="1">
+        <v>46050</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C131">
+        <v>1</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -4858,20 +4359,16 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="A132" s="1">
+        <v>46038</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C132">
+        <v>3</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4895,20 +4392,16 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-01-17</t>
-        </is>
+      <c r="A133" s="1">
+        <v>46039</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C133">
+        <v>3</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -4932,20 +4425,16 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="A134" s="1">
+        <v>46037</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C134">
+        <v>4</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -4969,20 +4458,16 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
+      <c r="A135" s="1">
+        <v>46027</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C135">
+        <v>4</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -5006,20 +4491,16 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
+      <c r="A136" s="1">
+        <v>46028</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C136">
+        <v>4</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -5043,20 +4524,16 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
+      <c r="A137" s="1">
+        <v>46046</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C137">
+        <v>4</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -5080,20 +4557,16 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
+      <c r="A138" s="1">
+        <v>46030</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C138">
+        <v>2</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -5117,20 +4590,16 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="A139" s="1">
+        <v>46023</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C139">
+        <v>1</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -5154,20 +4623,16 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
+      <c r="A140" s="1">
+        <v>46046</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C140">
+        <v>3</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -5191,20 +4656,16 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="A141" s="1">
+        <v>46045</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C141">
+        <v>4</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -5228,20 +4689,16 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-01-09</t>
-        </is>
+      <c r="A142" s="1">
+        <v>46031</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C142">
+        <v>4</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -5265,20 +4722,16 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="A143" s="1">
+        <v>46034</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C143">
+        <v>2</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -5302,20 +4755,16 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
+      <c r="A144" s="1">
+        <v>46024</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C144">
+        <v>4</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -5339,20 +4788,16 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
+      <c r="A145" s="1">
+        <v>46041</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C145">
+        <v>2</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -5376,20 +4821,16 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
+      <c r="A146" s="1">
+        <v>46029</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C146">
+        <v>1</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -5413,20 +4854,16 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
+      <c r="A147" s="1">
+        <v>46040</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C147">
+        <v>3</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -5450,20 +4887,16 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
+      <c r="A148" s="1">
+        <v>46040</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C148">
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -5487,20 +4920,16 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
+      <c r="A149" s="1">
+        <v>46029</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C149">
+        <v>3</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -5524,20 +4953,16 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
+      <c r="A150" s="1">
+        <v>46036</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C150">
+        <v>1</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -5561,20 +4986,16 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
+      <c r="A151" s="1">
+        <v>46029</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C151">
+        <v>4</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -5598,20 +5019,16 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
+      <c r="A152" s="1">
+        <v>46081</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C152">
+        <v>4</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -5635,20 +5052,16 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="A153" s="1">
+        <v>46055</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C153">
+        <v>2</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -5672,20 +5085,16 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
+      <c r="A154" s="1">
+        <v>46060</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C154">
+        <v>3</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -5709,20 +5118,16 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
+      <c r="A155" s="1">
+        <v>46064</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C155">
+        <v>2</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -5746,20 +5151,16 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="A156" s="1">
+        <v>46057</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C156">
+        <v>1</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -5783,20 +5184,16 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
+      <c r="A157" s="1">
+        <v>46067</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C157">
+        <v>2</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -5820,20 +5217,16 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
+      <c r="A158" s="1">
+        <v>46060</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C158">
+        <v>4</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -5857,20 +5250,16 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="A159" s="1">
+        <v>46055</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C159">
+        <v>2</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -5894,20 +5283,16 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
+      <c r="A160" s="1">
+        <v>46070</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C160">
+        <v>4</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -5931,20 +5316,16 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
+      <c r="A161" s="1">
+        <v>46074</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C161">
+        <v>4</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -5968,20 +5349,16 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
+      <c r="A162" s="1">
+        <v>46065</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C162">
+        <v>1</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -6005,20 +5382,16 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
+      <c r="A163" s="1">
+        <v>46068</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C163">
+        <v>2</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -6042,20 +5415,16 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
+      <c r="A164" s="1">
+        <v>46058</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C164">
+        <v>3</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -6079,20 +5448,16 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="A165" s="1">
+        <v>46055</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C165">
+        <v>2</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -6116,20 +5481,16 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
+      <c r="A166" s="1">
+        <v>46060</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C166">
+        <v>3</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -6153,20 +5514,16 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="A167" s="1">
+        <v>46059</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C167">
+        <v>4</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -6190,20 +5547,16 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
+      <c r="A168" s="1">
+        <v>46069</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C168">
+        <v>1</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -6227,20 +5580,16 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
+      <c r="A169" s="1">
+        <v>46072</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C169">
+        <v>2</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -6264,20 +5613,16 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="A170" s="1">
+        <v>46059</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C170">
+        <v>2</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -6301,20 +5646,16 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
+      <c r="A171" s="1">
+        <v>46072</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C171">
+        <v>2</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -6338,20 +5679,16 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
+      <c r="A172" s="1">
+        <v>46075</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C172">
+        <v>1</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -6375,20 +5712,16 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
+      <c r="A173" s="1">
+        <v>46071</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C173">
+        <v>3</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -6412,20 +5745,16 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
+      <c r="A174" s="1">
+        <v>46109</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C174">
+        <v>3</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -6449,20 +5778,16 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
+      <c r="A175" s="1">
+        <v>46086</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C175">
+        <v>4</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -6486,20 +5811,16 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
+      <c r="A176" s="1">
+        <v>46099</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C176">
+        <v>1</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -6523,20 +5844,16 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
+      <c r="A177" s="1">
+        <v>46083</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C177">
+        <v>2</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -6560,20 +5877,16 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
+      <c r="A178" s="1">
+        <v>46103</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C178">
+        <v>1</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -6597,20 +5910,16 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
+      <c r="A179" s="1">
+        <v>46091</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C179">
+        <v>4</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -6634,20 +5943,16 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
+      <c r="A180" s="1">
+        <v>46088</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C180">
+        <v>1</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -6671,20 +5976,16 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
+      <c r="A181" s="1">
+        <v>46103</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C181">
+        <v>3</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -6708,20 +6009,16 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
+      <c r="A182" s="1">
+        <v>46086</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C182">
+        <v>4</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -6745,20 +6042,16 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
+      <c r="A183" s="1">
+        <v>46106</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C183">
+        <v>4</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -6782,20 +6075,16 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
+      <c r="A184" s="1">
+        <v>46090</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C184">
+        <v>3</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -6819,20 +6108,16 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
+      <c r="A185" s="1">
+        <v>46089</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C185">
+        <v>1</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -6856,20 +6141,16 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="A186" s="1">
+        <v>46082</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C186">
+        <v>4</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -6893,20 +6174,16 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
+      <c r="A187" s="1">
+        <v>46085</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C187">
+        <v>1</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -6930,20 +6207,16 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
+      <c r="A188" s="1">
+        <v>46089</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C188">
+        <v>4</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -6967,20 +6240,16 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
+      <c r="A189" s="1">
+        <v>46085</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C189">
+        <v>2</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -7004,20 +6273,16 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
+      <c r="A190" s="1">
+        <v>46093</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C190">
+        <v>1</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -7041,20 +6306,16 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
+      <c r="A191" s="1">
+        <v>46104</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C191">
+        <v>4</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -7078,20 +6339,16 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
+      <c r="A192" s="1">
+        <v>46107</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C192">
+        <v>3</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -7115,20 +6372,16 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
+      <c r="A193" s="1">
+        <v>46084</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C193">
+        <v>2</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -7152,20 +6405,16 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
+      <c r="A194" s="1">
+        <v>46102</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C194">
+        <v>2</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -7189,20 +6438,16 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
+      <c r="A195" s="1">
+        <v>46140</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C195">
+        <v>4</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -7226,20 +6471,16 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
+      <c r="A196" s="1">
+        <v>46136</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C196">
+        <v>2</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -7263,20 +6504,16 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
+      <c r="A197" s="1">
+        <v>46130</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C197">
+        <v>1</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -7300,20 +6537,16 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
+      <c r="A198" s="1">
+        <v>46129</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C198">
+        <v>2</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -7337,20 +6570,16 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
+      <c r="A199" s="1">
+        <v>46137</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C199">
+        <v>1</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -7374,20 +6603,16 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
+      <c r="A200" s="1">
+        <v>46119</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C200">
+        <v>4</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -7411,20 +6636,16 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
+      <c r="A201" s="1">
+        <v>46133</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C201">
+        <v>4</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -7448,20 +6669,16 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
+      <c r="A202" s="1">
+        <v>46129</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C202">
+        <v>4</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -7485,20 +6702,16 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
+      <c r="A203" s="1">
+        <v>46124</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C203">
+        <v>4</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -7522,20 +6735,16 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
+      <c r="A204" s="1">
+        <v>46123</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C204">
+        <v>4</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -7559,20 +6768,16 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
+      <c r="A205" s="1">
+        <v>46114</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C205">
+        <v>4</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -7596,20 +6801,16 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
+      <c r="A206" s="1">
+        <v>46124</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C206">
+        <v>1</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -7633,20 +6834,16 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
+      <c r="A207" s="1">
+        <v>46128</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C207">
+        <v>4</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -7670,20 +6867,16 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
+      <c r="A208" s="1">
+        <v>46123</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C208">
+        <v>2</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -7707,20 +6900,16 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
+      <c r="A209" s="1">
+        <v>46124</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C209">
+        <v>4</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -7744,20 +6933,16 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
+      <c r="A210" s="1">
+        <v>46115</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C210">
+        <v>1</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -7781,20 +6966,16 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
+      <c r="A211" s="1">
+        <v>46118</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C211">
+        <v>1</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -7818,20 +6999,16 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
+      <c r="A212" s="1">
+        <v>46117</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C212">
+        <v>1</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -7855,20 +7032,16 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
+      <c r="A213" s="1">
+        <v>46132</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C213">
+        <v>2</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -7892,20 +7065,16 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
+      <c r="A214" s="1">
+        <v>46133</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C214">
+        <v>3</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -7929,20 +7098,16 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
+      <c r="A215" s="1">
+        <v>46138</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C215">
+        <v>3</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -7966,20 +7131,16 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
+      <c r="A216" s="1">
+        <v>46121</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C216">
+        <v>3</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -8003,20 +7164,16 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
+      <c r="A217" s="1">
+        <v>46170</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C217">
+        <v>4</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -8040,20 +7197,16 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
+      <c r="A218" s="1">
+        <v>46145</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C218">
+        <v>1</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -8077,20 +7230,16 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
+      <c r="A219" s="1">
+        <v>46154</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C219">
+        <v>3</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -8114,20 +7263,16 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
+      <c r="A220" s="1">
+        <v>46156</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C220">
+        <v>2</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -8151,20 +7296,16 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
+      <c r="A221" s="1">
+        <v>46153</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C221">
+        <v>2</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -8188,20 +7329,16 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
+      <c r="A222" s="1">
+        <v>46165</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C222">
+        <v>2</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -8225,20 +7362,16 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
+      <c r="A223" s="1">
+        <v>46165</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C223">
+        <v>3</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -8262,20 +7395,16 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
+      <c r="A224" s="1">
+        <v>46152</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C224">
+        <v>1</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -8299,20 +7428,16 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
+      <c r="A225" s="1">
+        <v>46167</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C225">
+        <v>3</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -8336,20 +7461,16 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
+      <c r="A226" s="1">
+        <v>46143</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C226">
+        <v>3</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -8373,20 +7494,16 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
+      <c r="A227" s="1">
+        <v>46156</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C227">
+        <v>1</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -8410,20 +7527,16 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
+      <c r="A228" s="1">
+        <v>46151</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C228">
+        <v>4</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -8447,20 +7560,16 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+      <c r="A229" s="1">
+        <v>46160</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C229">
+        <v>2</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -8484,20 +7593,16 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
+      <c r="A230" s="1">
+        <v>46158</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C230">
+        <v>2</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -8521,20 +7626,16 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
+      <c r="A231" s="1">
+        <v>46145</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C231">
+        <v>2</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -8558,20 +7659,16 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
+      <c r="A232" s="1">
+        <v>46150</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C232">
+        <v>2</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -8595,20 +7692,16 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
+      <c r="A233" s="1">
+        <v>46144</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C233">
+        <v>1</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -8632,20 +7725,16 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
+      <c r="A234" s="1">
+        <v>46165</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C234">
+        <v>1</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -8669,20 +7758,16 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
+      <c r="A235" s="1">
+        <v>46159</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C235">
+        <v>2</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -8706,20 +7791,16 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
+      <c r="A236" s="1">
+        <v>46167</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C236">
+        <v>2</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -8743,20 +7824,16 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
+      <c r="A237" s="1">
+        <v>46146</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C237">
+        <v>2</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -8780,20 +7857,16 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
+      <c r="A238" s="1">
+        <v>46201</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C238">
+        <v>3</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -8817,20 +7890,16 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
+      <c r="A239" s="1">
+        <v>46183</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C239">
+        <v>1</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -8854,20 +7923,16 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
+      <c r="A240" s="1">
+        <v>46175</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C240">
+        <v>2</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -8891,20 +7956,16 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+      <c r="A241" s="1">
+        <v>46192</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C241">
+        <v>4</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -8928,20 +7989,16 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
+      <c r="A242" s="1">
+        <v>46193</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C242">
+        <v>3</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -8965,20 +8022,16 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
+      <c r="A243" s="1">
+        <v>46176</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C243">
+        <v>1</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -9002,20 +8055,16 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
+      <c r="A244" s="1">
+        <v>46190</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C244">
+        <v>4</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -9039,20 +8088,16 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
+      <c r="A245" s="1">
+        <v>46178</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C245">
+        <v>2</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -9076,20 +8121,16 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
+      <c r="A246" s="1">
+        <v>46177</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C246">
+        <v>3</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -9113,20 +8154,16 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
+      <c r="A247" s="1">
+        <v>46183</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C247">
+        <v>2</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -9150,20 +8187,16 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
+      <c r="A248" s="1">
+        <v>46197</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C248">
+        <v>4</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -9187,20 +8220,16 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
+      <c r="A249" s="1">
+        <v>46190</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C249">
+        <v>3</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -9224,20 +8253,16 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
+      <c r="A250" s="1">
+        <v>46193</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C250">
+        <v>1</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -9261,20 +8286,16 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
+      <c r="A251" s="1">
+        <v>46196</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C251">
+        <v>2</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -9298,20 +8319,16 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="A252" s="1">
+        <v>46174</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C252">
+        <v>4</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -9335,20 +8352,16 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+      <c r="A253" s="1">
+        <v>46192</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C253">
+        <v>1</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -9372,20 +8385,16 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
+      <c r="A254" s="1">
+        <v>46189</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C254">
+        <v>4</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -9409,20 +8418,16 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
+      <c r="A255" s="1">
+        <v>46180</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C255">
+        <v>3</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -9446,20 +8451,16 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
+      <c r="A256" s="1">
+        <v>46183</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C256">
+        <v>3</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -9483,20 +8484,16 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
+      <c r="A257" s="1">
+        <v>46193</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C257">
+        <v>2</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -9520,20 +8517,16 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
+      <c r="A258" s="1">
+        <v>46182</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C258">
+        <v>3</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -9557,20 +8550,16 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+      <c r="A259" s="1">
+        <v>46191</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C259">
+        <v>1</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -9594,20 +8583,16 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+      <c r="A260" s="1">
+        <v>46231</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C260">
+        <v>1</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -9631,20 +8616,16 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
+      <c r="A261" s="1">
+        <v>46205</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C261">
+        <v>2</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -9668,20 +8649,16 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
+      <c r="A262" s="1">
+        <v>46228</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C262">
+        <v>2</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -9705,20 +8682,16 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
+      <c r="A263" s="1">
+        <v>46224</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C263">
+        <v>2</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -9742,20 +8715,16 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
+      <c r="A264" s="1">
+        <v>46211</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C264">
+        <v>4</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -9779,20 +8748,16 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
+      <c r="A265" s="1">
+        <v>46211</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C265">
+        <v>1</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -9816,20 +8781,16 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
+      <c r="A266" s="1">
+        <v>46222</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C266">
+        <v>2</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -9853,20 +8814,16 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
+      <c r="A267" s="1">
+        <v>46211</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C267">
+        <v>2</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -9890,20 +8847,16 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
+      <c r="A268" s="1">
+        <v>46227</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C268">
+        <v>4</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -9927,20 +8880,16 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
+      <c r="A269" s="1">
+        <v>46209</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C269">
+        <v>4</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -9964,20 +8913,16 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
+      <c r="A270" s="1">
+        <v>46207</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C270">
+        <v>3</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -10001,20 +8946,16 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
+      <c r="A271" s="1">
+        <v>46216</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C271">
+        <v>3</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -10038,20 +8979,16 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
+      <c r="A272" s="1">
+        <v>46216</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C272">
+        <v>1</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -10075,20 +9012,16 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
+      <c r="A273" s="1">
+        <v>46215</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C273">
+        <v>4</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -10112,20 +9045,16 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
+      <c r="A274" s="1">
+        <v>46212</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C274">
+        <v>2</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -10149,20 +9078,16 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
+      <c r="A275" s="1">
+        <v>46217</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C275">
+        <v>1</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -10186,20 +9111,16 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
+      <c r="A276" s="1">
+        <v>46207</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C276">
+        <v>3</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -10223,20 +9144,16 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
+      <c r="A277" s="1">
+        <v>46226</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C277">
+        <v>1</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -10260,20 +9177,16 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
+      <c r="A278" s="1">
+        <v>46221</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C278">
+        <v>1</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -10297,20 +9210,16 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
+      <c r="A279" s="1">
+        <v>46227</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C279">
+        <v>1</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -10334,20 +9243,16 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
+      <c r="A280" s="1">
+        <v>46216</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C280">
+        <v>1</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -10371,20 +9276,16 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
+      <c r="A281" s="1">
+        <v>46262</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C281">
+        <v>4</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -10408,20 +9309,16 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+      <c r="A282" s="1">
+        <v>46241</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C282">
+        <v>3</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -10445,20 +9342,16 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
+      <c r="A283" s="1">
+        <v>46259</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C283">
+        <v>2</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -10482,20 +9375,16 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
+      <c r="A284" s="1">
+        <v>46235</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C284">
+        <v>4</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -10519,20 +9408,16 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+      <c r="A285" s="1">
+        <v>46242</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C285">
+        <v>3</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -10556,20 +9441,16 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+      <c r="A286" s="1">
+        <v>46241</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C286">
+        <v>3</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -10593,20 +9474,16 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
+      <c r="A287" s="1">
+        <v>46244</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C287">
+        <v>3</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -10630,20 +9507,16 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
+      <c r="A288" s="1">
+        <v>46238</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C288">
+        <v>3</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -10667,20 +9540,16 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+      <c r="A289" s="1">
+        <v>46246</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C289">
+        <v>2</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -10704,20 +9573,16 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
+      <c r="A290" s="1">
+        <v>46251</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C290">
+        <v>4</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -10741,20 +9606,16 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
+      <c r="A291" s="1">
+        <v>46250</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C291">
+        <v>2</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -10778,20 +9639,16 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
+      <c r="A292" s="1">
+        <v>46258</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C292">
+        <v>3</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -10815,20 +9672,16 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
+      <c r="A293" s="1">
+        <v>46253</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C293">
+        <v>2</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -10852,20 +9705,16 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+      <c r="A294" s="1">
+        <v>46248</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C294">
+        <v>1</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -10889,20 +9738,16 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
+      <c r="A295" s="1">
+        <v>46258</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C295">
+        <v>2</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -10926,20 +9771,16 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
+      <c r="A296" s="1">
+        <v>46260</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C296">
+        <v>3</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -10963,20 +9804,16 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
+      <c r="A297" s="1">
+        <v>46247</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C297">
+        <v>1</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -11000,20 +9837,16 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+      <c r="A298" s="1">
+        <v>46240</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C298">
+        <v>1</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -11037,20 +9870,16 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
+      <c r="A299" s="1">
+        <v>46243</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C299">
+        <v>2</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -11074,20 +9903,16 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
+      <c r="A300" s="1">
+        <v>46239</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C300">
+        <v>3</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -11111,20 +9936,16 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+      <c r="A301" s="1">
+        <v>46241</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Träningsjacka</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C301">
+        <v>1</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
